--- a/config.xlsx
+++ b/config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29556235-707B-4D6C-A3FB-96FDEE64A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5E6376-E649-4771-ABF3-7BE2E4876578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -169,6 +169,9 @@
     <t>gebruiker</t>
   </si>
   <si>
+    <t>middenkolom</t>
+  </si>
+  <si>
     <t>Latijn-PN1-C1  Theātrum</t>
   </si>
   <si>
@@ -223,9 +226,6 @@
     <t>Grieks</t>
   </si>
   <si>
-    <t>Frans-VIZ5-10-Voilà mon école</t>
-  </si>
-  <si>
     <t>Frans</t>
   </si>
   <si>
@@ -235,10 +235,7 @@
     <t>Wim</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>F</t>
+    <t>Nee</t>
   </si>
   <si>
     <t>favoriet</t>
@@ -250,10 +247,46 @@
     <t>Pegasus Novus 1</t>
   </si>
   <si>
-    <t>Frans-VIZ5-11-Voilà mon école</t>
-  </si>
-  <si>
-    <t>Frans-VIZ5-12-Voilà mon école</t>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-1-12</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-1</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-2</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-3</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-4</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-5</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-6</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-7</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-8</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-9</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-10</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-11</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-12</t>
   </si>
 </sst>
 </file>
@@ -631,9 +664,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -661,7 +694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -675,7 +708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -689,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -703,7 +736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -728,14 +761,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -746,7 +779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -757,7 +790,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -768,7 +801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -779,7 +812,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -790,7 +823,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -801,7 +834,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -822,14 +855,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -857,16 +891,19 @@
       <c r="I1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -878,7 +915,7 @@
         <v>131</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -886,16 +923,19 @@
       <c r="I2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -907,7 +947,7 @@
         <v>216</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -915,16 +955,19 @@
       <c r="I3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -936,7 +979,7 @@
         <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -944,16 +987,19 @@
       <c r="I4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -962,7 +1008,7 @@
         <v>305</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -970,16 +1016,19 @@
       <c r="I5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -991,7 +1040,7 @@
         <v>384</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -999,16 +1048,19 @@
       <c r="I6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1020,7 +1072,7 @@
         <v>473</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -1028,16 +1080,19 @@
       <c r="I7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1049,7 +1104,7 @@
         <v>557</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -1057,16 +1112,19 @@
       <c r="I8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>306</v>
@@ -1075,7 +1133,7 @@
         <v>557</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -1083,16 +1141,19 @@
       <c r="I9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1101,7 +1162,7 @@
         <v>557</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -1109,16 +1170,19 @@
       <c r="I10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1130,7 +1194,7 @@
         <v>617</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -1138,16 +1202,19 @@
       <c r="I11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -1159,7 +1226,7 @@
         <v>688</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -1167,16 +1234,19 @@
       <c r="I12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13">
         <v>558</v>
@@ -1185,7 +1255,7 @@
         <v>688</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -1193,16 +1263,19 @@
       <c r="I13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1211,7 +1284,7 @@
         <v>688</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1219,16 +1292,19 @@
       <c r="I14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -1240,7 +1316,7 @@
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -1248,10 +1324,13 @@
       <c r="I15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
         <v>67</v>
@@ -1260,16 +1339,16 @@
         <v>68</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -1277,10 +1356,13 @@
       <c r="I16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
         <v>67</v>
@@ -1289,16 +1371,16 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
         <v>18</v>
@@ -1306,10 +1388,13 @@
       <c r="I17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
@@ -1318,16 +1403,16 @@
         <v>68</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
         <v>18</v>
@@ -1335,28 +1420,334 @@
       <c r="I18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="J18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>93</v>
+      </c>
+      <c r="F19">
+        <v>128</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>129</v>
+      </c>
+      <c r="F20">
+        <v>155</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" t="s">
-        <v>4</v>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>156</v>
+      </c>
+      <c r="F21">
+        <v>192</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>193</v>
+      </c>
+      <c r="F22">
+        <v>224</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>225</v>
+      </c>
+      <c r="F23">
+        <v>253</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>254</v>
+      </c>
+      <c r="F24">
+        <v>282</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25">
+        <v>283</v>
+      </c>
+      <c r="F25">
+        <v>313</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26">
+        <v>11</v>
+      </c>
+      <c r="E26">
+        <v>314</v>
+      </c>
+      <c r="F26">
+        <v>345</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>346</v>
+      </c>
+      <c r="F27">
+        <v>373</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>346</v>
+      </c>
+      <c r="F28">
+        <v>373</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I16 A19:I19 B17:I17 B18:I18" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A15:I15 B25:D25 B26:D26 B27:D27 A4:I14 A2:I2 A3:I3 G25:I25 G26:I26 G27:I27" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1364,11 +1755,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
         <v>47</v>
@@ -1383,10 +1774,10 @@
         <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1394,10 +1785,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1406,7 +1797,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1414,10 +1805,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3">
         <v>1</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5E6376-E649-4771-ABF3-7BE2E4876578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D051A6-D727-4124-A015-021003E0B530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="89">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Frans-VIZ5-12</t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-6-11</t>
   </si>
 </sst>
 </file>
@@ -855,7 +858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
@@ -1722,11 +1725,8 @@
       <c r="C28" t="s">
         <v>68</v>
       </c>
-      <c r="D28">
-        <v>12</v>
-      </c>
       <c r="E28">
-        <v>346</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>373</v>
@@ -1741,6 +1741,35 @@
         <v>4</v>
       </c>
       <c r="J28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29">
+        <v>156</v>
+      </c>
+      <c r="F29">
+        <v>373</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
         <v>70</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D051A6-D727-4124-A015-021003E0B530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEB3C7F-FBE0-4CCA-82B5-9CC22F60CC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="91">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -290,6 +290,12 @@
   </si>
   <si>
     <t>Frans-VIZ5-6-11</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-13</t>
+  </si>
+  <si>
+    <t>Van In Zouff 6</t>
   </si>
 </sst>
 </file>
@@ -858,7 +864,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
@@ -1770,6 +1776,38 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>70</v>
+      </c>
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
         <v>70</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEB3C7F-FBE0-4CCA-82B5-9CC22F60CC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A13820-A110-40BD-8E3A-DAB78D41AF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -756,13 +756,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D4 A6:C6 A5:C5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A13820-A110-40BD-8E3A-DAB78D41AF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E8E1A1-9553-40D2-B84B-FC92A92E2AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1802,7 @@
         <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I30" t="s">
         <v>4</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E8E1A1-9553-40D2-B84B-FC92A92E2AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062F2AEC-ED17-4F1F-A050-372A05E77D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22980" yWindow="3540" windowWidth="21430" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Van In Zouff 6</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-13w</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
@@ -1796,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
         <v>52</v>
@@ -1808,6 +1811,38 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>22</v>
+      </c>
+      <c r="F31">
+        <v>70</v>
+      </c>
+      <c r="G31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
         <v>70</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062F2AEC-ED17-4F1F-A050-372A05E77D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6989A2B5-6484-42EC-B4B2-071638991953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22980" yWindow="3540" windowWidth="21430" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="670" yWindow="3080" windowWidth="21430" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
     <t>Van In Zouff 6</t>
   </si>
   <si>
-    <t>Frans-VIZ6-13w</t>
+    <t>Frans-VIZ6-113</t>
   </si>
 </sst>
 </file>
@@ -1825,13 +1825,13 @@
         <v>90</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
         <v>52</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6989A2B5-6484-42EC-B4B2-071638991953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDACB26-75CB-4432-A07F-1E4DB9AD164E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="670" yWindow="3080" windowWidth="21430" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="96">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -298,7 +298,19 @@
     <t>Van In Zouff 6</t>
   </si>
   <si>
-    <t>Frans-VIZ6-113</t>
+    <t>$2b$10$/qbt62nWF/I/6ng5BoQIpuL19dNs9toCvqWj0jevVOK8I5b5AsggO</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>mieke.helsen@denegensprong.kobart.be</t>
+  </si>
+  <si>
+    <t>DeNegensprong-6A</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-13-ww</t>
   </si>
 </sst>
 </file>
@@ -675,10 +687,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -691,8 +708,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -706,7 +726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -720,7 +740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -734,7 +754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -748,7 +768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -760,6 +780,23 @@
       </c>
       <c r="D6" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1853,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDACB26-75CB-4432-A07F-1E4DB9AD164E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F89CAD6-477C-4A29-9720-71368E438894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="670" yWindow="3080" windowWidth="21430" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25920" yWindow="2150" windowWidth="21430" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="102">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -298,9 +298,6 @@
     <t>Van In Zouff 6</t>
   </si>
   <si>
-    <t>$2b$10$/qbt62nWF/I/6ng5BoQIpuL19dNs9toCvqWj0jevVOK8I5b5AsggO</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
@@ -311,6 +308,27 @@
   </si>
   <si>
     <t>Frans-VIZ6-13-ww</t>
+  </si>
+  <si>
+    <t>DeNegensprong-6B</t>
+  </si>
+  <si>
+    <t>DeNegensprong-5A</t>
+  </si>
+  <si>
+    <t>DeNegensprong-5B</t>
+  </si>
+  <si>
+    <t>$2b$10$yDvD5k.acOiXasYzK5m0K.LmFfnoabrBhdqxOp0LPHzEnApha8rGu</t>
+  </si>
+  <si>
+    <t>$2b$10$4h5nHo.0Hu/ycxZB6SOGVepLaFlB4sxRvsgYKh/tr..cr5ss6AiHS</t>
+  </si>
+  <si>
+    <t>$2b$10$bR10dRQrIuDQi6/jJm7zoeywP2x/k89GqE.7l57N5wavqJFeytFJa</t>
+  </si>
+  <si>
+    <t>$2b$10$3xxdYnI/E42D/CMv.uWy0ObB32qbXuJoX3k836u8tSVZFr.0XVAGW</t>
   </si>
 </sst>
 </file>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
@@ -695,7 +713,7 @@
     <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -709,10 +727,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -726,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -740,7 +758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -754,7 +772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -768,7 +786,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -782,12 +800,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -796,7 +814,52 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1853,7 +1916,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F89CAD6-477C-4A29-9720-71368E438894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784E0178-836C-4AFC-B931-E0F302C7C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25920" yWindow="2150" windowWidth="21430" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="103">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>$2b$10$3xxdYnI/E42D/CMv.uWy0ObB32qbXuJoX3k836u8tSVZFr.0XVAGW</t>
+  </si>
+  <si>
+    <t>wim@myntuus.be</t>
   </si>
 </sst>
 </file>
@@ -814,7 +817,7 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
         <v>92</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784E0178-836C-4AFC-B931-E0F302C7C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BBFB90-7594-499A-A128-6D3FEFE336E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25920" yWindow="2150" windowWidth="21430" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23170" yWindow="2090" windowWidth="21430" windowHeight="16740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="109">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -331,7 +331,25 @@
     <t>$2b$10$3xxdYnI/E42D/CMv.uWy0ObB32qbXuJoX3k836u8tSVZFr.0XVAGW</t>
   </si>
   <si>
-    <t>wim@myntuus.be</t>
+    <t>Frans-VIZ6-14</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-14-ww</t>
+  </si>
+  <si>
+    <t>finne.dierckx@denegensprong.kobart.be</t>
+  </si>
+  <si>
+    <t>linda.timmermans@denegensprong.kobart.be</t>
+  </si>
+  <si>
+    <t>joke.meeuwesen@denegensprong.kobart.be</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-15</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-15-ww</t>
   </si>
 </sst>
 </file>
@@ -708,15 +726,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,7 +752,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -747,7 +766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -761,7 +780,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -775,7 +794,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -789,7 +808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -803,7 +822,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -817,13 +836,10 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -836,8 +852,11 @@
       <c r="D8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -850,8 +869,11 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -863,6 +885,9 @@
       </c>
       <c r="D10" t="s">
         <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +995,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
@@ -1928,7 +1953,7 @@
         <v>90</v>
       </c>
       <c r="D31">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1946,6 +1971,134 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33">
+        <v>140</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>63</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34">
+        <v>14</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>140</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
         <v>70</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BBFB90-7594-499A-A128-6D3FEFE336E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537AF3F8-45B9-43C9-80F5-DAD8765A93D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23170" yWindow="2090" windowWidth="21430" windowHeight="16740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20830" yWindow="1720" windowWidth="21430" windowHeight="16740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="112">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -350,6 +350,15 @@
   </si>
   <si>
     <t>Frans-VIZ6-15-ww</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-16</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-16-ww</t>
+  </si>
+  <si>
+    <t>Frans-VIZ6-17</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.08203125" bestFit="1" customWidth="1"/>
@@ -2049,7 +2058,7 @@
         <v>90</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2081,7 +2090,7 @@
         <v>90</v>
       </c>
       <c r="D35">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2099,6 +2108,102 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36">
+        <v>16</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>28</v>
+      </c>
+      <c r="G36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>4</v>
+      </c>
+      <c r="J36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37">
+        <v>160</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" t="s">
+        <v>4</v>
+      </c>
+      <c r="J37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38">
+        <v>17</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
         <v>70</v>
       </c>
     </row>
